--- a/docs/xlsx/jobs-2026-08-12.xlsx
+++ b/docs/xlsx/jobs-2026-08-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="1112">
   <si>
     <t>Title</t>
   </si>
@@ -61,6 +61,24 @@
     <t>https://www.conservationjobboard.com/job-listing-abandoned-mine-crew-carson-city-nevada/2884719340</t>
   </si>
   <si>
+    <t>Adult Litter Crew Supervisor</t>
+  </si>
+  <si>
+    <t>WA State Department of Ecology</t>
+  </si>
+  <si>
+    <t>Spokane, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$3,738 - $4,866 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-adult-litter-crew-supervisor-spokane-washington/6128396178</t>
+  </si>
+  <si>
     <t>AmeriCorps Crew Member</t>
   </si>
   <si>
@@ -91,6 +109,24 @@
     <t>https://www.conservationjobboard.com/job-listing-americorps-crew-member-boise-idaho/7335697597</t>
   </si>
   <si>
+    <t>AmeriCorps Individual Placement - Recreation Technician</t>
+  </si>
+  <si>
+    <t>Southeast Conservation Corps</t>
+  </si>
+  <si>
+    <t>Edgefield, SC</t>
+  </si>
+  <si>
+    <t>$800 per week</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-individual-placement---recreation-technician-edgefield-south-carolina/5688938125</t>
+  </si>
+  <si>
     <t>Baltimore County Transit-Oriented Development Organizer</t>
   </si>
   <si>
@@ -100,9 +136,6 @@
     <t>Washington, DC</t>
   </si>
   <si>
-    <t>Temporary</t>
-  </si>
-  <si>
     <t>$30 - $34 per hour</t>
   </si>
   <si>
@@ -148,6 +181,24 @@
     <t>https://www.conservationjobboard.com/job-listing-campaign-associate-for-environmental-non-profit-washington-dc/7137599326</t>
   </si>
   <si>
+    <t>Chemist I/II</t>
+  </si>
+  <si>
+    <t>City of San Jose Environmental Services Department</t>
+  </si>
+  <si>
+    <t>San Jose, CA</t>
+  </si>
+  <si>
+    <t>$107,562 - $144,012 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chemist-iii-san-jose-california/3527249868</t>
+  </si>
+  <si>
     <t>Conservation Corps North Carolina-Program Coordinator</t>
   </si>
   <si>
@@ -184,6 +235,24 @@
     <t>https://www.conservationjobboard.com/job-listing-conservation-managerconservation-director-walla-walla-washington/5894825590</t>
   </si>
   <si>
+    <t>Conservation Project Manager</t>
+  </si>
+  <si>
+    <t>Howard Ecoworks</t>
+  </si>
+  <si>
+    <t>Columbia, MD</t>
+  </si>
+  <si>
+    <t>$52,000 - $56,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-project-manager-columbia-maryland/5749824018</t>
+  </si>
+  <si>
     <t>Contracts and Procurement Associate Specialist</t>
   </si>
   <si>
@@ -202,6 +271,39 @@
     <t>https://www.conservationjobboard.com/job-listing-contracts-and-procurement-associate-specialist-na--remote-montana/5379389886</t>
   </si>
   <si>
+    <t>Director of Advancement</t>
+  </si>
+  <si>
+    <t>Berkshire Natural Resources Council</t>
+  </si>
+  <si>
+    <t>Lenox, MA</t>
+  </si>
+  <si>
+    <t>$115,000 - $130,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-advancement-lenox-massachusetts/1778641910</t>
+  </si>
+  <si>
+    <t>Ecologist</t>
+  </si>
+  <si>
+    <t>Marin Water</t>
+  </si>
+  <si>
+    <t>Fairfax, CA</t>
+  </si>
+  <si>
+    <t>$8,638 - $12,218 per month</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecologist-fairfax-california/1557297281</t>
+  </si>
+  <si>
     <t>Ecozone Gardener</t>
   </si>
   <si>
@@ -238,6 +340,45 @@
     <t>https://www.conservationjobboard.com/job-listing-education-assistant-concord-new-hampshire/2226898051</t>
   </si>
   <si>
+    <t>Education Internship</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Wildlife Alliance</t>
+  </si>
+  <si>
+    <t>Sedalia, CO</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Unpaid Internship</t>
+  </si>
+  <si>
+    <t>environmental-education-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-internship-sedalia-colorado/9424959947</t>
+  </si>
+  <si>
+    <t>Environmental Conservation Program Manager</t>
+  </si>
+  <si>
+    <t>City of Austin</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>$80,490 - $102,200 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-conservation-program-manager-austin-texas/8651149776</t>
+  </si>
+  <si>
     <t>Environmental Education Internship</t>
   </si>
   <si>
@@ -253,9 +394,6 @@
     <t>$400 per month</t>
   </si>
   <si>
-    <t>environmental-education-wildlife</t>
-  </si>
-  <si>
     <t>https://www.conservationjobboard.com/job-listing-environmental-education-internship-glen-rose-texas/6916987148</t>
   </si>
   <si>
@@ -274,6 +412,24 @@
     <t>https://www.conservationjobboard.com/job-listing-environmental-educator-for-the-wow-mobile-classroom-internship-fort-myers-florida/4015856708</t>
   </si>
   <si>
+    <t>Environmental Scientist</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>$4,418 - $9,321 per month</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-scientist-san-diego-california/4813488857</t>
+  </si>
+  <si>
     <t>Environmental/Landscape Crew Member</t>
   </si>
   <si>
@@ -286,9 +442,6 @@
     <t>$24 - $30 per hour</t>
   </si>
   <si>
-    <t>general-stewardship-restoration</t>
-  </si>
-  <si>
     <t>https://www.conservationjobboard.com/job-listing-environmentallandscape-crew-member-sandwich-massachusetts/6589792855</t>
   </si>
   <si>
@@ -361,6 +514,21 @@
     <t>https://www.conservationjobboard.com/job-listing-farm-bill-biologist-north-vernon-indiana/6099736330</t>
   </si>
   <si>
+    <t>Farmer Interpreter</t>
+  </si>
+  <si>
+    <t>Old Grove Orange</t>
+  </si>
+  <si>
+    <t>Redlands, CA</t>
+  </si>
+  <si>
+    <t>$18 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-farmer-interpreter-redlands-california/2794658625</t>
+  </si>
+  <si>
     <t>Field Biologist</t>
   </si>
   <si>
@@ -400,6 +568,24 @@
     <t>https://www.conservationjobboard.com/job-listing-field-office-directo-madison-wisconsin/3869092288</t>
   </si>
   <si>
+    <t>Minneapolis, MN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-office-director-minneapolis-minnesota/5312971176</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-office-director-washington-dc/3299365343</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-office-director-los-angeles-california/7022284053</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-office-director-boston-massachusetts/4318345214</t>
+  </si>
+  <si>
     <t>Field Organizer</t>
   </si>
   <si>
@@ -430,6 +616,81 @@
     <t>https://www.conservationjobboard.com/job-listing-field-technician-san-luis-obispo-california/7970545083</t>
   </si>
   <si>
+    <t>Fisheries Technician 1- CWT Recovery Survey Lead</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Lodi, CA</t>
+  </si>
+  <si>
+    <t>$19.49 - $31.83 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-technician-1--cwt-recovery-survey-lead-lodi-california/1520582390</t>
+  </si>
+  <si>
+    <t>Fisheries Technician 1- CWT Recovery Surveys</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-technician-1--cwt-recovery-surveys-lodi-california/9253200615</t>
+  </si>
+  <si>
+    <t>Fishery Biologist/Biometrician</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$80,465 - $125,378 per year</t>
+  </si>
+  <si>
+    <t>ecology-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fishery-biologistbiometrician-portland-oregon/3816800418</t>
+  </si>
+  <si>
+    <t>Forest Field Technician I</t>
+  </si>
+  <si>
+    <t>Mountain Studies Institute</t>
+  </si>
+  <si>
+    <t>Durango, CO</t>
+  </si>
+  <si>
+    <t>$18 - $20 per hour</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-field-technician-i-durango-colorado/2153403112</t>
+  </si>
+  <si>
+    <t>Forest Roads Manager</t>
+  </si>
+  <si>
+    <t>Quinault Indian Nation</t>
+  </si>
+  <si>
+    <t>Taholah, WA</t>
+  </si>
+  <si>
+    <t>$78,412 - $109,776 per year</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-roads-manager-taholah-washington/5597927491</t>
+  </si>
+  <si>
     <t>Gorilla Reintroduction Project Volunteer</t>
   </si>
   <si>
@@ -439,9 +700,6 @@
     <t>Gabon, Africa</t>
   </si>
   <si>
-    <t>Unpaid</t>
-  </si>
-  <si>
     <t>Voluntary position</t>
   </si>
   <si>
@@ -454,15 +712,36 @@
     <t>Sustainable Northwest</t>
   </si>
   <si>
-    <t>Portland, OR</t>
-  </si>
-  <si>
     <t>$80,500 - $91,000 per year</t>
   </si>
   <si>
     <t>https://www.conservationjobboard.com/job-listing-granta-and-contract-senior-manager-portland-oregon/4000890341</t>
   </si>
   <si>
+    <t>Harvest Section Manager</t>
+  </si>
+  <si>
+    <t>$86,253 - $120,754 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-harvest-section-manager-taholah-washington/7767079924</t>
+  </si>
+  <si>
+    <t>Hatchery Operations Manager - Region 4 Central - WMS Band 2 - Permanent - 2026-06664</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Sultan, WA</t>
+  </si>
+  <si>
+    <t>$110,424 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hatchery-operations-manager---region-4-central---wms-band-2---permanent---2026-06664-sultan-washington/7706887718</t>
+  </si>
+  <si>
     <t>IL Farm Bill Wildlife Biologist I or II</t>
   </si>
   <si>
@@ -481,6 +760,42 @@
     <t>https://www.conservationjobboard.com/job-listing-il-farm-bill-wildlife-biologist-i-or-ii-normal-illinois/3886614212</t>
   </si>
   <si>
+    <t>Invasives Species Technician Member - AmeriCorps Individual Placement</t>
+  </si>
+  <si>
+    <t>Canaveral National Seashore, FL</t>
+  </si>
+  <si>
+    <t>$700 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-invasives-species-technician-member---americorps-individual-placement-canaveral-national-seashore-florida/6775397620</t>
+  </si>
+  <si>
+    <t>Invasives Species Technician Team Lead - AmeriCorps Individual Placement</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-invasives-species-technician-team-lead---americorps-individual-placement-canaveral-national-seashore-florida/6121163911</t>
+  </si>
+  <si>
+    <t>Land Stewardship Coordinator</t>
+  </si>
+  <si>
+    <t>Golden State Land Conservancy</t>
+  </si>
+  <si>
+    <t>Santa Rosa, CA</t>
+  </si>
+  <si>
+    <t>$80,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-stewardship-coordinator-santa-rosa-california/2978098564</t>
+  </si>
+  <si>
     <t>Legal Assistant - Real Property Specialist</t>
   </si>
   <si>
@@ -499,6 +814,36 @@
     <t>https://www.conservationjobboard.com/job-listing-legal-assistant---real-property-specialist-flexible-remote/7303133744</t>
   </si>
   <si>
+    <t>Lincoln National Forest Project Coordinator</t>
+  </si>
+  <si>
+    <t>Ruidoso, NM</t>
+  </si>
+  <si>
+    <t>$75,000 - $86,250 per year</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lincoln-national-forest-project-coordinator-ruidoso-new-mexico/3519342864</t>
+  </si>
+  <si>
+    <t>Marketing Specialist</t>
+  </si>
+  <si>
+    <t>Wyoming Game &amp; Fish</t>
+  </si>
+  <si>
+    <t>Cheyenne, WY</t>
+  </si>
+  <si>
+    <t>$27.39 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marketing-specialist-cheyenne-wyoming/7013005399</t>
+  </si>
+  <si>
     <t>MN Farm Bill Wildlife Biologist I, II, or III</t>
   </si>
   <si>
@@ -529,6 +874,24 @@
     <t>https://www.conservationjobboard.com/job-listing-native-seed-farm-technician-usfws-stillwater-national-wildlife-refuge-reno-nevada/4548576095</t>
   </si>
   <si>
+    <t>Natural Resource Project Manager</t>
+  </si>
+  <si>
+    <t>F4 Tech</t>
+  </si>
+  <si>
+    <t>Charlotte Harbor Area - SW Florida, FL</t>
+  </si>
+  <si>
+    <t>Pay is very competitive and commensurate along with the successful candidate’s education/experience while given the responsibilities of the position.</t>
+  </si>
+  <si>
+    <t>botany-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resource-project-manager-charlotte-harbor-florida/2529867083</t>
+  </si>
+  <si>
     <t>NCC Staff Crew Lead</t>
   </si>
   <si>
@@ -544,6 +907,30 @@
     <t>https://www.conservationjobboard.com/job-listing-ncc-staff-crew-lead-las-vegas-nevada/4884711976</t>
   </si>
   <si>
+    <t>Nonprofit Advocacy Jobs</t>
+  </si>
+  <si>
+    <t>Canvassing staff earn a base pay of $18.00 per hour, plus can earn 20% of what they raise over our minimum fundraising standard, giving staff the opportunity to earn more than $20 per hour.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nonprofit-advocacy-jobs-oakland-california/6343050047</t>
+  </si>
+  <si>
+    <t>Operations &amp; Finance Coordinator</t>
+  </si>
+  <si>
+    <t>30 Mile River Watershed Association</t>
+  </si>
+  <si>
+    <t>Mt. Vernon, ME</t>
+  </si>
+  <si>
+    <t>$22 - $27 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations--finance-coordinator-mt-vernon-maine/7062207197</t>
+  </si>
+  <si>
     <t>Outdoor Education Instructor</t>
   </si>
   <si>
@@ -598,18 +985,87 @@
     <t>Pre-Sale Forester</t>
   </si>
   <si>
-    <t>Quinault Indian Nation</t>
-  </si>
-  <si>
-    <t>Taholah, WA</t>
-  </si>
-  <si>
     <t>$58,912 - $82,477 per year</t>
   </si>
   <si>
     <t>https://www.conservationjobboard.com/job-listing-pre-sale-forester-taholah-washington/2662496072</t>
   </si>
   <si>
+    <t>Production &amp; Collections Data Manager</t>
+  </si>
+  <si>
+    <t>Native Seed, LP</t>
+  </si>
+  <si>
+    <t>Winters, CA</t>
+  </si>
+  <si>
+    <t>$24 - $33.65 per hour</t>
+  </si>
+  <si>
+    <t>botany-general-stewardship-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-production--collections-data-manager-winters-california/5356580233</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-coordinator-old-fort-north-carolina/4554209997</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>National Association of Conservation Districts (NACD)</t>
+  </si>
+  <si>
+    <t>$75,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-manager-washington-dc-dc/7262943969</t>
+  </si>
+  <si>
+    <t>Range Ecologist</t>
+  </si>
+  <si>
+    <t>National Audubon Society</t>
+  </si>
+  <si>
+    <t>North Platte, NE</t>
+  </si>
+  <si>
+    <t>$57,100 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-range-ecologist-north-platte-nebraska/8059659950</t>
+  </si>
+  <si>
+    <t>Regional Fisheries Supervisor</t>
+  </si>
+  <si>
+    <t>$7,184.67 - $7,983.73 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-fisheries-supervisor-cheyenne-wyoming/5867385784</t>
+  </si>
+  <si>
+    <t>Resource Specialist</t>
+  </si>
+  <si>
+    <t>Bernalillo County</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>$22.81 - $36.01 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resource-specialist-albuquerque-new-mexico/3266311045</t>
+  </si>
+  <si>
     <t>Restoration and Invasive Species Management Field Operations Manager</t>
   </si>
   <si>
@@ -637,9 +1093,6 @@
     <t>Commensurate with Experience</t>
   </si>
   <si>
-    <t>hydrology-restoration</t>
-  </si>
-  <si>
     <t>https://www.conservationjobboard.com/job-listing-restoration-biologist-big-cypress-reservation-florida/8141426871</t>
   </si>
   <si>
@@ -658,6 +1111,36 @@
     <t>https://www.conservationjobboard.com/job-listing-school-year-program-instructor-20262027-san-gregorio-california/1515329741</t>
   </si>
   <si>
+    <t>Scientist I - Ecologist (Stream and Wetland Restoration)</t>
+  </si>
+  <si>
+    <t>Resource Environmental Solutions, LLC</t>
+  </si>
+  <si>
+    <t>Nashville, TN</t>
+  </si>
+  <si>
+    <t>Salary based on experience</t>
+  </si>
+  <si>
+    <t>botany-hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-scientist-i---ecologist-stream-and-wetland-restoration-nashville-tennessee/3910094086</t>
+  </si>
+  <si>
+    <t>Senior Program Manager, Salton Sea</t>
+  </si>
+  <si>
+    <t>Palm Desert, CA</t>
+  </si>
+  <si>
+    <t>$85,600 - $96,300 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-program-manager-salton-sea-palm-desert-california/3509428847</t>
+  </si>
+  <si>
     <t>Shareholder Advocate for Environmentally Responsible Mutual Fund</t>
   </si>
   <si>
@@ -703,6 +1186,9 @@
     <t>https://www.conservationjobboard.com/job-listing-sustainability-campaigner-miami-florida/2823116717</t>
   </si>
   <si>
+    <t>https://www.conservationjobboard.com/job-listing-sustainability-campaigner-portland-oregon/4459436721</t>
+  </si>
+  <si>
     <t>Trail Maintenance Technician</t>
   </si>
   <si>
@@ -748,6 +1234,33 @@
     <t>https://www.conservationjobboard.com/job-listing-tropical-field-research-intern-rivas-costa-rica-latin-america/6210429362</t>
   </si>
   <si>
+    <t>Vice President and Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Buzzards Bay Coalition</t>
+  </si>
+  <si>
+    <t>New Bedford, MA</t>
+  </si>
+  <si>
+    <t>$220,000 - $250,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president-and-chief-financial-officer-new-bedford-massachusetts/7929527890</t>
+  </si>
+  <si>
+    <t>Wetlands and Riparian Protection Unit Supervisor</t>
+  </si>
+  <si>
+    <t>$10,854 - $13,493 per month</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wetlands-and-riparian-protection-unit-supervisor-san-diego-california/9816287642</t>
+  </si>
+  <si>
     <t>ACLU-NC Immigrants' Rights Staff Attorney</t>
   </si>
   <si>
@@ -838,9 +1351,6 @@
     <t>BRL 8356.00 - 8356.00/month</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/bc0cb0d168cf4b48be0a07c340964aca-analista-de-projetos-senior-instituto-brasileiro-de-defesa-do-consumidor-sao-paulo</t>
   </si>
   <si>
@@ -2266,9 +2776,6 @@
     <t>https://www.idealist.org/en/nonprofit-job/417fb1dca3b7480697118aa4037cadf3-program-associate-nyc-community-interpreter-bank-training-engagement-outreach-the-new-york-immigration-coalition-new-york</t>
   </si>
   <si>
-    <t>Program Coordinator</t>
-  </si>
-  <si>
     <t>Bethesda Project</t>
   </si>
   <si>
@@ -2308,9 +2815,6 @@
     <t>https://www.idealist.org/en/nonprofit-job/d1e67b13cdab4353b8db828c35278f30-program-lead-north-america-seismic-foundation-washington</t>
   </si>
   <si>
-    <t>Program Manager</t>
-  </si>
-  <si>
     <t>National Association of Conservation Districts</t>
   </si>
   <si>
@@ -2561,9 +3065,6 @@
   </si>
   <si>
     <t>Senior Director, Leadership Giving</t>
-  </si>
-  <si>
-    <t>National Audubon Society</t>
   </si>
   <si>
     <t>Oakland, California</t>
@@ -3234,7 +3735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3313,99 +3814,99 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>41</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>42</v>
@@ -3413,292 +3914,292 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
         <v>50</v>
       </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>57</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" t="s">
         <v>59</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
         <v>62</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
         <v>65</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
         <v>68</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>70</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
         <v>71</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
         <v>74</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>75</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
         <v>76</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>77</v>
       </c>
-      <c r="E14" t="s">
+      <c r="H14" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="F14" t="s">
-        <v>79</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
         <v>81</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
         <v>82</v>
       </c>
-      <c r="C15" t="s">
+      <c r="F15" t="s">
         <v>83</v>
       </c>
-      <c r="D15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="H15" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="F15" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
         <v>86</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>87</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="F16" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
         <v>92</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" t="s">
         <v>97</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>98</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" t="s">
         <v>100</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
         <v>103</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>104</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
         <v>105</v>
       </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>106</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
         <v>109</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>110</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>111</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
       </c>
       <c r="E20" t="s">
         <v>112</v>
@@ -3744,277 +4245,277 @@
         <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C26" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C29" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B31" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F31" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B32" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C32" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F33" t="s">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C34" t="s">
         <v>184</v>
@@ -4023,289 +4524,1209 @@
         <v>11</v>
       </c>
       <c r="E34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F34" t="s">
-        <v>72</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B35" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C35" t="s">
-        <v>189</v>
+        <v>39</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F35" t="s">
-        <v>191</v>
+        <v>41</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C36" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="C37" t="s">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="F37" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C38" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
-        <v>207</v>
+        <v>41</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="C39" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="F39" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B40" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>202</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="F40" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F41" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="C42" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F42" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F43" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C44" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="F44" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B45" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C45" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="E45" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="F45" t="s">
-        <v>232</v>
+        <v>47</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>230</v>
+      </c>
+      <c r="B46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C46" t="s">
+        <v>209</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>232</v>
+      </c>
+      <c r="F46" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>234</v>
+      </c>
+      <c r="B47" t="s">
+        <v>220</v>
+      </c>
+      <c r="C47" t="s">
+        <v>221</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>235</v>
+      </c>
+      <c r="F47" t="s">
+        <v>223</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>237</v>
+      </c>
+      <c r="B48" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" t="s">
         <v>239</v>
       </c>
-      <c r="B46" t="s">
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
         <v>240</v>
       </c>
-      <c r="C46" t="s">
+      <c r="F48" t="s">
+        <v>204</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D46" t="s">
-        <v>141</v>
-      </c>
-      <c r="E46" t="s">
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>242</v>
       </c>
-      <c r="F46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H46" s="2" t="s">
+      <c r="B49" t="s">
         <v>243</v>
+      </c>
+      <c r="C49" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>245</v>
+      </c>
+      <c r="F49" t="s">
+        <v>246</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>248</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>249</v>
+      </c>
+      <c r="D50" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" t="s">
+        <v>250</v>
+      </c>
+      <c r="F50" t="s">
+        <v>100</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>252</v>
+      </c>
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" t="s">
+        <v>249</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" t="s">
+        <v>34</v>
+      </c>
+      <c r="F51" t="s">
+        <v>100</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>254</v>
+      </c>
+      <c r="B52" t="s">
+        <v>255</v>
+      </c>
+      <c r="C52" t="s">
+        <v>256</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>257</v>
+      </c>
+      <c r="F52" t="s">
+        <v>258</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>260</v>
+      </c>
+      <c r="B53" t="s">
+        <v>261</v>
+      </c>
+      <c r="C53" t="s">
+        <v>262</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>263</v>
+      </c>
+      <c r="F53" t="s">
+        <v>264</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>266</v>
+      </c>
+      <c r="B54" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" t="s">
+        <v>267</v>
+      </c>
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" t="s">
+        <v>268</v>
+      </c>
+      <c r="F54" t="s">
+        <v>269</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>271</v>
+      </c>
+      <c r="B55" t="s">
+        <v>272</v>
+      </c>
+      <c r="C55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" t="s">
+        <v>274</v>
+      </c>
+      <c r="F55" t="s">
+        <v>83</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>276</v>
+      </c>
+      <c r="B56" t="s">
+        <v>243</v>
+      </c>
+      <c r="C56" t="s">
+        <v>277</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>278</v>
+      </c>
+      <c r="F56" t="s">
+        <v>246</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>280</v>
+      </c>
+      <c r="B57" t="s">
+        <v>281</v>
+      </c>
+      <c r="C57" t="s">
+        <v>282</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" t="s">
+        <v>283</v>
+      </c>
+      <c r="F57" t="s">
+        <v>284</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>286</v>
+      </c>
+      <c r="B58" t="s">
+        <v>287</v>
+      </c>
+      <c r="C58" t="s">
+        <v>288</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>289</v>
+      </c>
+      <c r="F58" t="s">
+        <v>290</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>292</v>
+      </c>
+      <c r="B59" t="s">
+        <v>293</v>
+      </c>
+      <c r="C59" t="s">
+        <v>294</v>
+      </c>
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>295</v>
+      </c>
+      <c r="F59" t="s">
+        <v>65</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>297</v>
+      </c>
+      <c r="B60" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" t="s">
+        <v>298</v>
+      </c>
+      <c r="F60" t="s">
+        <v>41</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>300</v>
+      </c>
+      <c r="B61" t="s">
+        <v>301</v>
+      </c>
+      <c r="C61" t="s">
+        <v>302</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>303</v>
+      </c>
+      <c r="F61" t="s">
+        <v>83</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>305</v>
+      </c>
+      <c r="B62" t="s">
+        <v>306</v>
+      </c>
+      <c r="C62" t="s">
+        <v>307</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
+        <v>308</v>
+      </c>
+      <c r="F62" t="s">
+        <v>309</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>311</v>
+      </c>
+      <c r="B63" t="s">
+        <v>312</v>
+      </c>
+      <c r="C63" t="s">
+        <v>313</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>314</v>
+      </c>
+      <c r="F63" t="s">
+        <v>106</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>316</v>
+      </c>
+      <c r="B64" t="s">
+        <v>317</v>
+      </c>
+      <c r="C64" t="s">
+        <v>318</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>319</v>
+      </c>
+      <c r="F64" t="s">
+        <v>320</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>322</v>
+      </c>
+      <c r="B65" t="s">
+        <v>220</v>
+      </c>
+      <c r="C65" t="s">
+        <v>221</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>323</v>
+      </c>
+      <c r="F65" t="s">
+        <v>29</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>325</v>
+      </c>
+      <c r="B66" t="s">
+        <v>326</v>
+      </c>
+      <c r="C66" t="s">
+        <v>327</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>328</v>
+      </c>
+      <c r="F66" t="s">
+        <v>329</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>331</v>
+      </c>
+      <c r="B67" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" t="s">
+        <v>63</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>64</v>
+      </c>
+      <c r="F67" t="s">
+        <v>65</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>333</v>
+      </c>
+      <c r="B68" t="s">
+        <v>334</v>
+      </c>
+      <c r="C68" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>335</v>
+      </c>
+      <c r="F68" t="s">
+        <v>65</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>337</v>
+      </c>
+      <c r="B69" t="s">
+        <v>338</v>
+      </c>
+      <c r="C69" t="s">
+        <v>339</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>340</v>
+      </c>
+      <c r="F69" t="s">
+        <v>164</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>342</v>
+      </c>
+      <c r="B70" t="s">
+        <v>272</v>
+      </c>
+      <c r="C70" t="s">
+        <v>273</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>343</v>
+      </c>
+      <c r="F70" t="s">
+        <v>204</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>345</v>
+      </c>
+      <c r="B71" t="s">
+        <v>346</v>
+      </c>
+      <c r="C71" t="s">
+        <v>347</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>348</v>
+      </c>
+      <c r="F71" t="s">
+        <v>158</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>350</v>
+      </c>
+      <c r="B72" t="s">
+        <v>351</v>
+      </c>
+      <c r="C72" t="s">
+        <v>352</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>353</v>
+      </c>
+      <c r="F72" t="s">
+        <v>77</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>355</v>
+      </c>
+      <c r="B73" t="s">
+        <v>356</v>
+      </c>
+      <c r="C73" t="s">
+        <v>357</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>358</v>
+      </c>
+      <c r="F73" t="s">
+        <v>136</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>360</v>
+      </c>
+      <c r="B74" t="s">
+        <v>361</v>
+      </c>
+      <c r="C74" t="s">
+        <v>362</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
+        <v>363</v>
+      </c>
+      <c r="F74" t="s">
+        <v>106</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>365</v>
+      </c>
+      <c r="B75" t="s">
+        <v>366</v>
+      </c>
+      <c r="C75" t="s">
+        <v>367</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s">
+        <v>368</v>
+      </c>
+      <c r="F75" t="s">
+        <v>369</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>371</v>
+      </c>
+      <c r="B76" t="s">
+        <v>338</v>
+      </c>
+      <c r="C76" t="s">
+        <v>372</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" t="s">
+        <v>373</v>
+      </c>
+      <c r="F76" t="s">
+        <v>47</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>375</v>
+      </c>
+      <c r="B77" t="s">
+        <v>376</v>
+      </c>
+      <c r="C77" t="s">
+        <v>51</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>377</v>
+      </c>
+      <c r="F77" t="s">
+        <v>378</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>380</v>
+      </c>
+      <c r="B78" t="s">
+        <v>381</v>
+      </c>
+      <c r="C78" t="s">
+        <v>382</v>
+      </c>
+      <c r="D78" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" t="s">
+        <v>383</v>
+      </c>
+      <c r="F78" t="s">
+        <v>384</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>380</v>
+      </c>
+      <c r="B79" t="s">
+        <v>381</v>
+      </c>
+      <c r="C79" t="s">
+        <v>386</v>
+      </c>
+      <c r="D79" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" t="s">
+        <v>383</v>
+      </c>
+      <c r="F79" t="s">
+        <v>384</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>380</v>
+      </c>
+      <c r="B80" t="s">
+        <v>381</v>
+      </c>
+      <c r="C80" t="s">
+        <v>388</v>
+      </c>
+      <c r="D80" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" t="s">
+        <v>383</v>
+      </c>
+      <c r="F80" t="s">
+        <v>384</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>380</v>
+      </c>
+      <c r="B81" t="s">
+        <v>381</v>
+      </c>
+      <c r="C81" t="s">
+        <v>209</v>
+      </c>
+      <c r="D81" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" t="s">
+        <v>383</v>
+      </c>
+      <c r="F81" t="s">
+        <v>384</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>391</v>
+      </c>
+      <c r="B82" t="s">
+        <v>392</v>
+      </c>
+      <c r="C82" t="s">
+        <v>393</v>
+      </c>
+      <c r="D82" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" t="s">
+        <v>314</v>
+      </c>
+      <c r="F82" t="s">
+        <v>394</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>396</v>
+      </c>
+      <c r="B83" t="s">
+        <v>397</v>
+      </c>
+      <c r="C83" t="s">
+        <v>398</v>
+      </c>
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s">
+        <v>399</v>
+      </c>
+      <c r="F83" t="s">
+        <v>394</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>401</v>
+      </c>
+      <c r="B84" t="s">
+        <v>402</v>
+      </c>
+      <c r="C84" t="s">
+        <v>403</v>
+      </c>
+      <c r="D84" t="s">
+        <v>111</v>
+      </c>
+      <c r="E84" t="s">
+        <v>404</v>
+      </c>
+      <c r="F84" t="s">
+        <v>47</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>406</v>
+      </c>
+      <c r="B85" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" t="s">
+        <v>408</v>
+      </c>
+      <c r="D85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s">
+        <v>409</v>
+      </c>
+      <c r="F85" t="s">
+        <v>83</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>411</v>
+      </c>
+      <c r="B86" t="s">
+        <v>133</v>
+      </c>
+      <c r="C86" t="s">
+        <v>134</v>
+      </c>
+      <c r="D86" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s">
+        <v>412</v>
+      </c>
+      <c r="F86" t="s">
+        <v>413</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -4356,6 +5777,46 @@
     <hyperlink ref="H44" r:id="rId43"/>
     <hyperlink ref="H45" r:id="rId44"/>
     <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4453,3544 +5914,3544 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>415</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>416</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>417</v>
       </c>
       <c r="D2" t="s">
-        <v>247</v>
+        <v>418</v>
       </c>
       <c r="E2" t="s">
-        <v>248</v>
+        <v>419</v>
       </c>
       <c r="F2" t="s">
-        <v>249</v>
+        <v>420</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>250</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>251</v>
+        <v>422</v>
       </c>
       <c r="B3" t="s">
-        <v>252</v>
+        <v>423</v>
       </c>
       <c r="C3" t="s">
-        <v>253</v>
+        <v>424</v>
       </c>
       <c r="D3" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E3" t="s">
-        <v>255</v>
+        <v>426</v>
       </c>
       <c r="F3" t="s">
-        <v>256</v>
+        <v>427</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>257</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>258</v>
+        <v>429</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>430</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D4" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E4" t="s">
-        <v>261</v>
+        <v>432</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
+        <v>433</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>263</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>435</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>436</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E5" t="s">
-        <v>267</v>
+        <v>438</v>
       </c>
       <c r="F5" t="s">
-        <v>268</v>
+        <v>439</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>269</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>270</v>
+        <v>441</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>442</v>
       </c>
       <c r="C6" t="s">
-        <v>272</v>
+        <v>443</v>
       </c>
       <c r="D6" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E6" t="s">
-        <v>273</v>
+        <v>444</v>
       </c>
       <c r="F6" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>275</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>446</v>
       </c>
       <c r="B7" t="s">
-        <v>277</v>
+        <v>447</v>
       </c>
       <c r="C7" t="s">
-        <v>278</v>
+        <v>448</v>
       </c>
       <c r="D7" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F7" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>280</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>281</v>
+        <v>451</v>
       </c>
       <c r="B8" t="s">
-        <v>282</v>
+        <v>452</v>
       </c>
       <c r="C8" t="s">
-        <v>283</v>
+        <v>453</v>
       </c>
       <c r="D8" t="s">
-        <v>247</v>
+        <v>418</v>
       </c>
       <c r="E8" t="s">
-        <v>284</v>
+        <v>454</v>
       </c>
       <c r="F8" t="s">
-        <v>285</v>
+        <v>455</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>286</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>287</v>
+        <v>457</v>
       </c>
       <c r="B9" t="s">
-        <v>288</v>
+        <v>458</v>
       </c>
       <c r="C9" t="s">
-        <v>289</v>
+        <v>459</v>
       </c>
       <c r="D9" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E9" t="s">
-        <v>290</v>
+        <v>460</v>
       </c>
       <c r="F9" t="s">
-        <v>291</v>
+        <v>461</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>292</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>293</v>
+        <v>463</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C10" t="s">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="D10" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E10" t="s">
-        <v>296</v>
+        <v>466</v>
       </c>
       <c r="F10" t="s">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>298</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>299</v>
+        <v>469</v>
       </c>
       <c r="B11" t="s">
-        <v>300</v>
+        <v>470</v>
       </c>
       <c r="C11" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="D11" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E11" t="s">
-        <v>302</v>
+        <v>472</v>
       </c>
       <c r="F11" t="s">
-        <v>303</v>
+        <v>473</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>304</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>305</v>
+        <v>475</v>
       </c>
       <c r="B12" t="s">
-        <v>306</v>
+        <v>476</v>
       </c>
       <c r="C12" t="s">
-        <v>307</v>
+        <v>477</v>
       </c>
       <c r="D12" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E12" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
       <c r="F12" t="s">
-        <v>309</v>
+        <v>479</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>310</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>311</v>
+        <v>481</v>
       </c>
       <c r="B13" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="D13" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E13" t="s">
-        <v>312</v>
+        <v>482</v>
       </c>
       <c r="F13" t="s">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>313</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>314</v>
+        <v>484</v>
       </c>
       <c r="B14" t="s">
-        <v>315</v>
+        <v>485</v>
       </c>
       <c r="C14" t="s">
-        <v>316</v>
+        <v>486</v>
       </c>
       <c r="D14" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E14" t="s">
-        <v>317</v>
+        <v>487</v>
       </c>
       <c r="F14" t="s">
-        <v>318</v>
+        <v>488</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>319</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>490</v>
       </c>
       <c r="B15" t="s">
-        <v>321</v>
+        <v>491</v>
       </c>
       <c r="C15" t="s">
-        <v>322</v>
+        <v>492</v>
       </c>
       <c r="D15" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E15" t="s">
-        <v>323</v>
+        <v>493</v>
       </c>
       <c r="F15" t="s">
-        <v>324</v>
+        <v>494</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>325</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>326</v>
+        <v>496</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>497</v>
       </c>
       <c r="C16" t="s">
-        <v>328</v>
+        <v>498</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E16" t="s">
-        <v>329</v>
+        <v>499</v>
       </c>
       <c r="F16" t="s">
-        <v>324</v>
+        <v>494</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>330</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>331</v>
+        <v>501</v>
       </c>
       <c r="B17" t="s">
-        <v>332</v>
+        <v>502</v>
       </c>
       <c r="C17" t="s">
-        <v>333</v>
+        <v>503</v>
       </c>
       <c r="D17" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E17" t="s">
-        <v>334</v>
+        <v>504</v>
       </c>
       <c r="F17" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>335</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>336</v>
+        <v>506</v>
       </c>
       <c r="B18" t="s">
-        <v>337</v>
+        <v>507</v>
       </c>
       <c r="C18" t="s">
-        <v>338</v>
+        <v>508</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E18" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F18" t="s">
-        <v>339</v>
+        <v>509</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>340</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>341</v>
+        <v>511</v>
       </c>
       <c r="B19" t="s">
-        <v>342</v>
+        <v>512</v>
       </c>
       <c r="C19" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D19" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E19" t="s">
-        <v>290</v>
+        <v>460</v>
       </c>
       <c r="F19" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>343</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>344</v>
+        <v>514</v>
       </c>
       <c r="B20" t="s">
-        <v>345</v>
+        <v>515</v>
       </c>
       <c r="C20" t="s">
-        <v>346</v>
+        <v>516</v>
       </c>
       <c r="D20" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E20" t="s">
-        <v>347</v>
+        <v>517</v>
       </c>
       <c r="F20" t="s">
-        <v>348</v>
+        <v>518</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>349</v>
+        <v>519</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>350</v>
+        <v>520</v>
       </c>
       <c r="B21" t="s">
-        <v>351</v>
+        <v>521</v>
       </c>
       <c r="C21" t="s">
-        <v>352</v>
+        <v>522</v>
       </c>
       <c r="D21" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E21" t="s">
-        <v>353</v>
+        <v>523</v>
       </c>
       <c r="F21" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>354</v>
+        <v>524</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>355</v>
+        <v>525</v>
       </c>
       <c r="B22" t="s">
-        <v>356</v>
+        <v>526</v>
       </c>
       <c r="C22" t="s">
-        <v>357</v>
+        <v>527</v>
       </c>
       <c r="D22" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E22" t="s">
-        <v>358</v>
+        <v>528</v>
       </c>
       <c r="F22" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>359</v>
+        <v>529</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>360</v>
+        <v>530</v>
       </c>
       <c r="B23" t="s">
-        <v>361</v>
+        <v>531</v>
       </c>
       <c r="C23" t="s">
-        <v>362</v>
+        <v>532</v>
       </c>
       <c r="D23" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E23" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F23" t="s">
-        <v>285</v>
+        <v>455</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>363</v>
+        <v>533</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>364</v>
+        <v>534</v>
       </c>
       <c r="B24" t="s">
-        <v>365</v>
+        <v>535</v>
       </c>
       <c r="C24" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="D24" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E24" t="s">
-        <v>366</v>
+        <v>536</v>
       </c>
       <c r="F24" t="s">
-        <v>367</v>
+        <v>537</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>368</v>
+        <v>538</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>369</v>
+        <v>539</v>
       </c>
       <c r="B25" t="s">
-        <v>370</v>
+        <v>540</v>
       </c>
       <c r="C25" t="s">
-        <v>371</v>
+        <v>541</v>
       </c>
       <c r="D25" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E25" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F25" t="s">
-        <v>372</v>
+        <v>542</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>373</v>
+        <v>543</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>374</v>
+        <v>544</v>
       </c>
       <c r="B26" t="s">
-        <v>375</v>
+        <v>545</v>
       </c>
       <c r="C26" t="s">
-        <v>376</v>
+        <v>546</v>
       </c>
       <c r="D26" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E26" t="s">
-        <v>377</v>
+        <v>547</v>
       </c>
       <c r="F26" t="s">
-        <v>378</v>
+        <v>548</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>379</v>
+        <v>549</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>380</v>
+        <v>550</v>
       </c>
       <c r="B27" t="s">
-        <v>381</v>
+        <v>551</v>
       </c>
       <c r="C27" t="s">
-        <v>382</v>
+        <v>552</v>
       </c>
       <c r="D27" t="s">
-        <v>383</v>
+        <v>553</v>
       </c>
       <c r="E27" t="s">
-        <v>384</v>
+        <v>554</v>
       </c>
       <c r="F27" t="s">
-        <v>385</v>
+        <v>555</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>386</v>
+        <v>556</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>387</v>
+        <v>557</v>
       </c>
       <c r="B28" t="s">
-        <v>388</v>
+        <v>558</v>
       </c>
       <c r="C28" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D28" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E28" t="s">
-        <v>389</v>
+        <v>559</v>
       </c>
       <c r="F28" t="s">
-        <v>390</v>
+        <v>560</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>391</v>
+        <v>561</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>392</v>
+        <v>562</v>
       </c>
       <c r="B29" t="s">
-        <v>393</v>
+        <v>563</v>
       </c>
       <c r="C29" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D29" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E29" t="s">
-        <v>395</v>
+        <v>565</v>
       </c>
       <c r="F29" t="s">
-        <v>396</v>
+        <v>566</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>397</v>
+        <v>567</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>398</v>
+        <v>568</v>
       </c>
       <c r="B30" t="s">
-        <v>399</v>
+        <v>569</v>
       </c>
       <c r="C30" t="s">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="D30" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E30" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F30" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>401</v>
+        <v>571</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>402</v>
+        <v>572</v>
       </c>
       <c r="B31" t="s">
-        <v>399</v>
+        <v>569</v>
       </c>
       <c r="C31" t="s">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="D31" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E31" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F31" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>403</v>
+        <v>573</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>404</v>
+        <v>574</v>
       </c>
       <c r="B32" t="s">
-        <v>405</v>
+        <v>575</v>
       </c>
       <c r="C32" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D32" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E32" t="s">
-        <v>406</v>
+        <v>576</v>
       </c>
       <c r="F32" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>407</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>408</v>
+        <v>578</v>
       </c>
       <c r="B33" t="s">
-        <v>409</v>
+        <v>579</v>
       </c>
       <c r="C33" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="D33" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E33" t="s">
-        <v>410</v>
+        <v>580</v>
       </c>
       <c r="F33" t="s">
-        <v>411</v>
+        <v>581</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>412</v>
+        <v>582</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>413</v>
+        <v>583</v>
       </c>
       <c r="B34" t="s">
-        <v>414</v>
+        <v>584</v>
       </c>
       <c r="C34" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D34" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E34" t="s">
-        <v>415</v>
+        <v>585</v>
       </c>
       <c r="F34" t="s">
-        <v>285</v>
+        <v>455</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>416</v>
+        <v>586</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>417</v>
+        <v>587</v>
       </c>
       <c r="B35" t="s">
-        <v>418</v>
+        <v>588</v>
       </c>
       <c r="C35" t="s">
-        <v>419</v>
+        <v>589</v>
       </c>
       <c r="D35" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E35" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F35" t="s">
-        <v>420</v>
+        <v>590</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>421</v>
+        <v>591</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>417</v>
+        <v>587</v>
       </c>
       <c r="B36" t="s">
-        <v>418</v>
+        <v>588</v>
       </c>
       <c r="C36" t="s">
-        <v>422</v>
+        <v>592</v>
       </c>
       <c r="D36" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E36" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F36" t="s">
-        <v>420</v>
+        <v>590</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>423</v>
+        <v>593</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>417</v>
+        <v>587</v>
       </c>
       <c r="B37" t="s">
-        <v>418</v>
+        <v>588</v>
       </c>
       <c r="C37" t="s">
-        <v>424</v>
+        <v>594</v>
       </c>
       <c r="D37" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E37" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F37" t="s">
-        <v>420</v>
+        <v>590</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>425</v>
+        <v>595</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>426</v>
+        <v>596</v>
       </c>
       <c r="B38" t="s">
-        <v>427</v>
+        <v>597</v>
       </c>
       <c r="C38" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D38" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E38" t="s">
-        <v>428</v>
+        <v>598</v>
       </c>
       <c r="F38" t="s">
-        <v>429</v>
+        <v>599</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>430</v>
+        <v>600</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>431</v>
+        <v>601</v>
       </c>
       <c r="B39" t="s">
-        <v>432</v>
+        <v>602</v>
       </c>
       <c r="C39" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D39" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E39" t="s">
-        <v>433</v>
+        <v>603</v>
       </c>
       <c r="F39" t="s">
-        <v>434</v>
+        <v>604</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>435</v>
+        <v>605</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>436</v>
+        <v>606</v>
       </c>
       <c r="B40" t="s">
-        <v>437</v>
+        <v>607</v>
       </c>
       <c r="C40" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D40" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E40" t="s">
-        <v>438</v>
+        <v>608</v>
       </c>
       <c r="F40" t="s">
-        <v>439</v>
+        <v>609</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>440</v>
+        <v>610</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>441</v>
+        <v>611</v>
       </c>
       <c r="B41" t="s">
-        <v>442</v>
+        <v>612</v>
       </c>
       <c r="C41" t="s">
-        <v>443</v>
+        <v>613</v>
       </c>
       <c r="D41" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E41" t="s">
-        <v>444</v>
+        <v>614</v>
       </c>
       <c r="F41" t="s">
-        <v>445</v>
+        <v>615</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>446</v>
+        <v>616</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>447</v>
+        <v>617</v>
       </c>
       <c r="B42" t="s">
-        <v>448</v>
+        <v>618</v>
       </c>
       <c r="C42" t="s">
-        <v>449</v>
+        <v>619</v>
       </c>
       <c r="D42" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E42" t="s">
-        <v>450</v>
+        <v>620</v>
       </c>
       <c r="F42" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>451</v>
+        <v>621</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>452</v>
+        <v>622</v>
       </c>
       <c r="B43" t="s">
-        <v>453</v>
+        <v>623</v>
       </c>
       <c r="C43" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D43" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E43" t="s">
-        <v>454</v>
+        <v>624</v>
       </c>
       <c r="F43" t="s">
-        <v>455</v>
+        <v>625</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>456</v>
+        <v>626</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>457</v>
+        <v>627</v>
       </c>
       <c r="B44" t="s">
-        <v>458</v>
+        <v>628</v>
       </c>
       <c r="C44" t="s">
-        <v>459</v>
+        <v>629</v>
       </c>
       <c r="D44" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E44" t="s">
-        <v>460</v>
+        <v>630</v>
       </c>
       <c r="F44" t="s">
-        <v>461</v>
+        <v>631</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>462</v>
+        <v>632</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>463</v>
+        <v>633</v>
       </c>
       <c r="B45" t="s">
-        <v>464</v>
+        <v>634</v>
       </c>
       <c r="C45" t="s">
-        <v>465</v>
+        <v>635</v>
       </c>
       <c r="D45" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E45" t="s">
-        <v>466</v>
+        <v>636</v>
       </c>
       <c r="F45" t="s">
-        <v>467</v>
+        <v>637</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>468</v>
+        <v>638</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>469</v>
+        <v>639</v>
       </c>
       <c r="B46" t="s">
-        <v>470</v>
+        <v>640</v>
       </c>
       <c r="C46" t="s">
-        <v>471</v>
+        <v>641</v>
       </c>
       <c r="D46" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E46" t="s">
-        <v>472</v>
+        <v>642</v>
       </c>
       <c r="F46" t="s">
-        <v>367</v>
+        <v>537</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>473</v>
+        <v>643</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>474</v>
+        <v>644</v>
       </c>
       <c r="B47" t="s">
-        <v>475</v>
+        <v>645</v>
       </c>
       <c r="C47" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D47" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E47" t="s">
-        <v>476</v>
+        <v>646</v>
       </c>
       <c r="F47" t="s">
-        <v>477</v>
+        <v>647</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>478</v>
+        <v>648</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>479</v>
+        <v>649</v>
       </c>
       <c r="B48" t="s">
-        <v>480</v>
+        <v>650</v>
       </c>
       <c r="C48" t="s">
-        <v>481</v>
+        <v>651</v>
       </c>
       <c r="D48" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E48" t="s">
-        <v>482</v>
+        <v>652</v>
       </c>
       <c r="F48" t="s">
-        <v>483</v>
+        <v>653</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>484</v>
+        <v>654</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>485</v>
+        <v>655</v>
       </c>
       <c r="B49" t="s">
-        <v>486</v>
+        <v>656</v>
       </c>
       <c r="C49" t="s">
-        <v>487</v>
+        <v>657</v>
       </c>
       <c r="D49" t="s">
-        <v>488</v>
+        <v>658</v>
       </c>
       <c r="E49" t="s">
-        <v>489</v>
+        <v>659</v>
       </c>
       <c r="F49" t="s">
-        <v>490</v>
+        <v>660</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>491</v>
+        <v>661</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>492</v>
+        <v>662</v>
       </c>
       <c r="B50" t="s">
-        <v>493</v>
+        <v>663</v>
       </c>
       <c r="C50" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D50" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E50" t="s">
-        <v>494</v>
+        <v>664</v>
       </c>
       <c r="F50" t="s">
-        <v>429</v>
+        <v>599</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>495</v>
+        <v>665</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>496</v>
+        <v>666</v>
       </c>
       <c r="B51" t="s">
-        <v>497</v>
+        <v>667</v>
       </c>
       <c r="C51" t="s">
-        <v>498</v>
+        <v>668</v>
       </c>
       <c r="D51" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E51" t="s">
-        <v>499</v>
+        <v>669</v>
       </c>
       <c r="F51" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>500</v>
+        <v>670</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>501</v>
+        <v>671</v>
       </c>
       <c r="B52" t="s">
-        <v>502</v>
+        <v>672</v>
       </c>
       <c r="C52" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D52" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E52" t="s">
-        <v>503</v>
+        <v>673</v>
       </c>
       <c r="F52" t="s">
-        <v>434</v>
+        <v>604</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>504</v>
+        <v>674</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="B53" t="s">
-        <v>505</v>
+        <v>675</v>
       </c>
       <c r="C53" t="s">
-        <v>506</v>
+        <v>676</v>
       </c>
       <c r="D53" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E53" t="s">
-        <v>507</v>
+        <v>677</v>
       </c>
       <c r="F53" t="s">
-        <v>508</v>
+        <v>678</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>509</v>
+        <v>679</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="B54" t="s">
-        <v>510</v>
+        <v>680</v>
       </c>
       <c r="C54" t="s">
-        <v>511</v>
+        <v>681</v>
       </c>
       <c r="D54" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E54" t="s">
-        <v>512</v>
+        <v>682</v>
       </c>
       <c r="F54" t="s">
-        <v>513</v>
+        <v>683</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>514</v>
+        <v>684</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>515</v>
+        <v>685</v>
       </c>
       <c r="B55" t="s">
-        <v>516</v>
+        <v>686</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="D55" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E55" t="s">
-        <v>517</v>
+        <v>687</v>
       </c>
       <c r="F55" t="s">
-        <v>518</v>
+        <v>688</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>519</v>
+        <v>689</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>520</v>
+        <v>690</v>
       </c>
       <c r="B56" t="s">
-        <v>521</v>
+        <v>691</v>
       </c>
       <c r="C56" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="D56" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E56" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F56" t="s">
-        <v>522</v>
+        <v>692</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>523</v>
+        <v>693</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>524</v>
+        <v>694</v>
       </c>
       <c r="B57" t="s">
-        <v>480</v>
+        <v>650</v>
       </c>
       <c r="C57" t="s">
-        <v>481</v>
+        <v>651</v>
       </c>
       <c r="D57" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E57" t="s">
-        <v>267</v>
+        <v>438</v>
       </c>
       <c r="F57" t="s">
-        <v>461</v>
+        <v>631</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>525</v>
+        <v>695</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>526</v>
+        <v>696</v>
       </c>
       <c r="B58" t="s">
-        <v>306</v>
+        <v>476</v>
       </c>
       <c r="C58" t="s">
-        <v>527</v>
+        <v>697</v>
       </c>
       <c r="D58" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E58" t="s">
-        <v>528</v>
+        <v>698</v>
       </c>
       <c r="F58" t="s">
-        <v>309</v>
+        <v>479</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>529</v>
+        <v>699</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>530</v>
+        <v>700</v>
       </c>
       <c r="B59" t="s">
-        <v>306</v>
+        <v>476</v>
       </c>
       <c r="C59" t="s">
-        <v>531</v>
+        <v>701</v>
       </c>
       <c r="D59" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E59" t="s">
-        <v>528</v>
+        <v>698</v>
       </c>
       <c r="F59" t="s">
-        <v>309</v>
+        <v>479</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>532</v>
+        <v>702</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>533</v>
+        <v>703</v>
       </c>
       <c r="B60" t="s">
-        <v>534</v>
+        <v>704</v>
       </c>
       <c r="C60" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D60" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E60" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F60" t="s">
-        <v>535</v>
+        <v>705</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>536</v>
+        <v>706</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>537</v>
+        <v>707</v>
       </c>
       <c r="B61" t="s">
-        <v>538</v>
+        <v>708</v>
       </c>
       <c r="C61" t="s">
-        <v>539</v>
+        <v>709</v>
       </c>
       <c r="D61" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E61" t="s">
-        <v>540</v>
+        <v>710</v>
       </c>
       <c r="F61" t="s">
-        <v>541</v>
+        <v>711</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>542</v>
+        <v>712</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>543</v>
+        <v>713</v>
       </c>
       <c r="B62" t="s">
-        <v>544</v>
+        <v>714</v>
       </c>
       <c r="C62" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D62" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E62" t="s">
-        <v>545</v>
+        <v>715</v>
       </c>
       <c r="F62" t="s">
-        <v>546</v>
+        <v>716</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>547</v>
+        <v>717</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>548</v>
+        <v>718</v>
       </c>
       <c r="B63" t="s">
-        <v>549</v>
+        <v>719</v>
       </c>
       <c r="C63" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D63" t="s">
+        <v>658</v>
+      </c>
+      <c r="E63" t="s">
+        <v>720</v>
+      </c>
+      <c r="F63" t="s">
         <v>488</v>
       </c>
-      <c r="E63" t="s">
-        <v>550</v>
-      </c>
-      <c r="F63" t="s">
-        <v>318</v>
-      </c>
       <c r="H63" s="2" t="s">
-        <v>551</v>
+        <v>721</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>552</v>
+        <v>722</v>
       </c>
       <c r="B64" t="s">
-        <v>553</v>
+        <v>723</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>424</v>
       </c>
       <c r="D64" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E64" t="s">
-        <v>554</v>
+        <v>724</v>
       </c>
       <c r="F64" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>555</v>
+        <v>725</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>556</v>
+        <v>726</v>
       </c>
       <c r="B65" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C65" t="s">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="D65" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E65" t="s">
-        <v>312</v>
+        <v>482</v>
       </c>
       <c r="F65" t="s">
-        <v>557</v>
+        <v>727</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>558</v>
+        <v>728</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>559</v>
+        <v>729</v>
       </c>
       <c r="B66" t="s">
-        <v>560</v>
+        <v>730</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>209</v>
       </c>
       <c r="D66" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E66" t="s">
-        <v>561</v>
+        <v>731</v>
       </c>
       <c r="F66" t="s">
-        <v>562</v>
+        <v>732</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>563</v>
+        <v>733</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>564</v>
+        <v>734</v>
       </c>
       <c r="B67" t="s">
-        <v>399</v>
+        <v>569</v>
       </c>
       <c r="C67" t="s">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="D67" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E67" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F67" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>565</v>
+        <v>735</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>566</v>
+        <v>736</v>
       </c>
       <c r="B68" t="s">
-        <v>567</v>
+        <v>737</v>
       </c>
       <c r="C68" t="s">
-        <v>253</v>
+        <v>424</v>
       </c>
       <c r="D68" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E68" t="s">
-        <v>568</v>
+        <v>738</v>
       </c>
       <c r="F68" t="s">
-        <v>569</v>
+        <v>739</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>570</v>
+        <v>740</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>571</v>
+        <v>741</v>
       </c>
       <c r="B69" t="s">
-        <v>572</v>
+        <v>742</v>
       </c>
       <c r="C69" t="s">
-        <v>266</v>
+        <v>437</v>
       </c>
       <c r="D69" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E69" t="s">
-        <v>573</v>
+        <v>743</v>
       </c>
       <c r="F69" t="s">
-        <v>574</v>
+        <v>744</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>575</v>
+        <v>745</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>576</v>
+        <v>746</v>
       </c>
       <c r="B70" t="s">
-        <v>399</v>
+        <v>569</v>
       </c>
       <c r="C70" t="s">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="D70" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E70" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F70" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>577</v>
+        <v>747</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>578</v>
+        <v>748</v>
       </c>
       <c r="B71" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C71" t="s">
-        <v>579</v>
+        <v>749</v>
       </c>
       <c r="D71" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E71" t="s">
-        <v>580</v>
+        <v>750</v>
       </c>
       <c r="F71" t="s">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>581</v>
+        <v>751</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>582</v>
+        <v>752</v>
       </c>
       <c r="B72" t="s">
-        <v>583</v>
+        <v>753</v>
       </c>
       <c r="C72" t="s">
-        <v>584</v>
+        <v>754</v>
       </c>
       <c r="D72" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E72" t="s">
-        <v>585</v>
+        <v>755</v>
       </c>
       <c r="F72" t="s">
-        <v>586</v>
+        <v>756</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>587</v>
+        <v>757</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>588</v>
+        <v>758</v>
       </c>
       <c r="B73" t="s">
-        <v>589</v>
+        <v>759</v>
       </c>
       <c r="C73" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D73" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E73" t="s">
-        <v>590</v>
+        <v>760</v>
       </c>
       <c r="F73" t="s">
-        <v>591</v>
+        <v>761</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>592</v>
+        <v>762</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>593</v>
+        <v>763</v>
       </c>
       <c r="B74" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C74" t="s">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="D74" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E74" t="s">
-        <v>312</v>
+        <v>482</v>
       </c>
       <c r="F74" t="s">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>594</v>
+        <v>764</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>595</v>
+        <v>765</v>
       </c>
       <c r="B75" t="s">
-        <v>596</v>
+        <v>766</v>
       </c>
       <c r="C75" t="s">
-        <v>597</v>
+        <v>767</v>
       </c>
       <c r="D75" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E75" t="s">
-        <v>598</v>
+        <v>768</v>
       </c>
       <c r="F75" t="s">
-        <v>599</v>
+        <v>769</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>600</v>
+        <v>770</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>601</v>
+        <v>771</v>
       </c>
       <c r="B76" t="s">
-        <v>602</v>
+        <v>772</v>
       </c>
       <c r="C76" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D76" t="s">
-        <v>247</v>
+        <v>418</v>
       </c>
       <c r="E76" t="s">
-        <v>603</v>
+        <v>773</v>
       </c>
       <c r="F76" t="s">
-        <v>604</v>
+        <v>774</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>605</v>
+        <v>775</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>606</v>
+        <v>776</v>
       </c>
       <c r="B77" t="s">
-        <v>607</v>
+        <v>777</v>
       </c>
       <c r="C77" t="s">
-        <v>376</v>
+        <v>546</v>
       </c>
       <c r="D77" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E77" t="s">
-        <v>608</v>
+        <v>778</v>
       </c>
       <c r="F77" t="s">
-        <v>609</v>
+        <v>779</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>610</v>
+        <v>780</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>611</v>
+        <v>781</v>
       </c>
       <c r="B78" t="s">
-        <v>612</v>
+        <v>782</v>
       </c>
       <c r="C78" t="s">
-        <v>613</v>
+        <v>783</v>
       </c>
       <c r="D78" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E78" t="s">
-        <v>614</v>
+        <v>784</v>
       </c>
       <c r="F78" t="s">
-        <v>615</v>
+        <v>785</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>616</v>
+        <v>786</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>617</v>
+        <v>787</v>
       </c>
       <c r="B79" t="s">
-        <v>618</v>
+        <v>788</v>
       </c>
       <c r="C79" t="s">
-        <v>465</v>
+        <v>635</v>
       </c>
       <c r="D79" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E79" t="s">
-        <v>619</v>
+        <v>789</v>
       </c>
       <c r="F79" t="s">
-        <v>620</v>
+        <v>790</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>621</v>
+        <v>791</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>617</v>
+        <v>787</v>
       </c>
       <c r="B80" t="s">
-        <v>618</v>
+        <v>788</v>
       </c>
       <c r="C80" t="s">
-        <v>253</v>
+        <v>424</v>
       </c>
       <c r="D80" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E80" t="s">
-        <v>619</v>
+        <v>789</v>
       </c>
       <c r="F80" t="s">
-        <v>620</v>
+        <v>790</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>622</v>
+        <v>792</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>617</v>
+        <v>787</v>
       </c>
       <c r="B81" t="s">
-        <v>618</v>
+        <v>788</v>
       </c>
       <c r="C81" t="s">
-        <v>623</v>
+        <v>793</v>
       </c>
       <c r="D81" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E81" t="s">
-        <v>619</v>
+        <v>789</v>
       </c>
       <c r="F81" t="s">
-        <v>620</v>
+        <v>790</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>624</v>
+        <v>794</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>625</v>
+        <v>795</v>
       </c>
       <c r="B82" t="s">
-        <v>626</v>
+        <v>796</v>
       </c>
       <c r="C82" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="D82" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E82" t="s">
-        <v>627</v>
+        <v>797</v>
       </c>
       <c r="F82" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>628</v>
+        <v>798</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>629</v>
+        <v>799</v>
       </c>
       <c r="B83" t="s">
-        <v>630</v>
+        <v>800</v>
       </c>
       <c r="C83" t="s">
-        <v>539</v>
+        <v>709</v>
       </c>
       <c r="D83" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E83" t="s">
-        <v>261</v>
+        <v>432</v>
       </c>
       <c r="F83" t="s">
-        <v>631</v>
+        <v>801</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>632</v>
+        <v>802</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>633</v>
+        <v>803</v>
       </c>
       <c r="B84" t="s">
-        <v>399</v>
+        <v>569</v>
       </c>
       <c r="C84" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D84" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E84" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F84" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>634</v>
+        <v>804</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>635</v>
+        <v>805</v>
       </c>
       <c r="B85" t="s">
-        <v>636</v>
+        <v>806</v>
       </c>
       <c r="C85" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D85" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E85" t="s">
-        <v>637</v>
+        <v>807</v>
       </c>
       <c r="F85" t="s">
-        <v>638</v>
+        <v>808</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>639</v>
+        <v>809</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>640</v>
+        <v>810</v>
       </c>
       <c r="B86" t="s">
-        <v>641</v>
+        <v>811</v>
       </c>
       <c r="C86" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D86" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E86" t="s">
-        <v>642</v>
+        <v>812</v>
       </c>
       <c r="F86" t="s">
-        <v>643</v>
+        <v>813</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>644</v>
+        <v>814</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>645</v>
+        <v>815</v>
       </c>
       <c r="B87" t="s">
-        <v>646</v>
+        <v>816</v>
       </c>
       <c r="C87" t="s">
-        <v>376</v>
+        <v>546</v>
       </c>
       <c r="D87" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E87" t="s">
-        <v>647</v>
+        <v>817</v>
       </c>
       <c r="F87" t="s">
-        <v>648</v>
+        <v>818</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>649</v>
+        <v>819</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>650</v>
+        <v>820</v>
       </c>
       <c r="B88" t="s">
-        <v>651</v>
+        <v>821</v>
       </c>
       <c r="C88" t="s">
-        <v>506</v>
+        <v>676</v>
       </c>
       <c r="D88" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E88" t="s">
-        <v>550</v>
+        <v>720</v>
       </c>
       <c r="F88" t="s">
-        <v>652</v>
+        <v>822</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>653</v>
+        <v>823</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>654</v>
+        <v>824</v>
       </c>
       <c r="B89" t="s">
-        <v>655</v>
+        <v>825</v>
       </c>
       <c r="C89" t="s">
-        <v>656</v>
+        <v>826</v>
       </c>
       <c r="D89" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E89" t="s">
-        <v>657</v>
+        <v>827</v>
       </c>
       <c r="F89" t="s">
-        <v>658</v>
+        <v>828</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>659</v>
+        <v>829</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>660</v>
+        <v>830</v>
       </c>
       <c r="B90" t="s">
-        <v>661</v>
+        <v>831</v>
       </c>
       <c r="C90" t="s">
-        <v>662</v>
+        <v>832</v>
       </c>
       <c r="D90" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E90" t="s">
-        <v>663</v>
+        <v>833</v>
       </c>
       <c r="F90" t="s">
-        <v>291</v>
+        <v>461</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>664</v>
+        <v>834</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>665</v>
+        <v>835</v>
       </c>
       <c r="B91" t="s">
-        <v>666</v>
+        <v>836</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D91" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E91" t="s">
-        <v>667</v>
+        <v>837</v>
       </c>
       <c r="F91" t="s">
-        <v>668</v>
+        <v>838</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>669</v>
+        <v>839</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>670</v>
+        <v>840</v>
       </c>
       <c r="B92" t="s">
-        <v>671</v>
+        <v>841</v>
       </c>
       <c r="C92" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D92" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E92" t="s">
-        <v>672</v>
+        <v>842</v>
       </c>
       <c r="F92" t="s">
-        <v>673</v>
+        <v>843</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>674</v>
+        <v>844</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>675</v>
+        <v>845</v>
       </c>
       <c r="B93" t="s">
-        <v>676</v>
+        <v>846</v>
       </c>
       <c r="C93" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D93" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E93" t="s">
-        <v>494</v>
+        <v>664</v>
       </c>
       <c r="F93" t="s">
-        <v>677</v>
+        <v>847</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>678</v>
+        <v>848</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>679</v>
+        <v>849</v>
       </c>
       <c r="B94" t="s">
-        <v>342</v>
+        <v>512</v>
       </c>
       <c r="C94" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D94" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E94" t="s">
-        <v>680</v>
+        <v>850</v>
       </c>
       <c r="F94" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>681</v>
+        <v>851</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>682</v>
+        <v>852</v>
       </c>
       <c r="B95" t="s">
-        <v>683</v>
+        <v>853</v>
       </c>
       <c r="C95" t="s">
-        <v>684</v>
+        <v>854</v>
       </c>
       <c r="D95" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E95" t="s">
-        <v>550</v>
+        <v>720</v>
       </c>
       <c r="F95" t="s">
-        <v>685</v>
+        <v>855</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>686</v>
+        <v>856</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>687</v>
+        <v>857</v>
       </c>
       <c r="B96" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C96" t="s">
-        <v>579</v>
+        <v>749</v>
       </c>
       <c r="D96" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E96" t="s">
-        <v>312</v>
+        <v>482</v>
       </c>
       <c r="F96" t="s">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>688</v>
+        <v>858</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>689</v>
+        <v>859</v>
       </c>
       <c r="B97" t="s">
-        <v>486</v>
+        <v>656</v>
       </c>
       <c r="C97" t="s">
-        <v>690</v>
+        <v>860</v>
       </c>
       <c r="D97" t="s">
-        <v>488</v>
+        <v>658</v>
       </c>
       <c r="E97" t="s">
-        <v>691</v>
+        <v>861</v>
       </c>
       <c r="F97" t="s">
-        <v>692</v>
+        <v>862</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>693</v>
+        <v>863</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>694</v>
+        <v>864</v>
       </c>
       <c r="B98" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C98" t="s">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="D98" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E98" t="s">
-        <v>695</v>
+        <v>865</v>
       </c>
       <c r="F98" t="s">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>696</v>
+        <v>866</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>697</v>
+        <v>867</v>
       </c>
       <c r="B99" t="s">
-        <v>698</v>
+        <v>868</v>
       </c>
       <c r="C99" t="s">
-        <v>699</v>
+        <v>869</v>
       </c>
       <c r="D99" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E99" t="s">
-        <v>700</v>
+        <v>870</v>
       </c>
       <c r="F99" t="s">
-        <v>429</v>
+        <v>599</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>701</v>
+        <v>871</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>702</v>
+        <v>872</v>
       </c>
       <c r="B100" t="s">
-        <v>703</v>
+        <v>873</v>
       </c>
       <c r="C100" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D100" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E100" t="s">
-        <v>704</v>
+        <v>874</v>
       </c>
       <c r="F100" t="s">
-        <v>262</v>
+        <v>433</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>705</v>
+        <v>875</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>706</v>
+        <v>876</v>
       </c>
       <c r="B101" t="s">
-        <v>707</v>
+        <v>877</v>
       </c>
       <c r="C101" t="s">
-        <v>708</v>
+        <v>878</v>
       </c>
       <c r="D101" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E101" t="s">
-        <v>709</v>
+        <v>879</v>
       </c>
       <c r="F101" t="s">
-        <v>710</v>
+        <v>880</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>711</v>
+        <v>881</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>712</v>
+        <v>882</v>
       </c>
       <c r="B102" t="s">
-        <v>713</v>
+        <v>883</v>
       </c>
       <c r="C102" t="s">
-        <v>714</v>
+        <v>884</v>
       </c>
       <c r="D102" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E102" t="s">
-        <v>715</v>
+        <v>885</v>
       </c>
       <c r="F102" t="s">
-        <v>716</v>
+        <v>886</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>717</v>
+        <v>887</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>718</v>
+        <v>888</v>
       </c>
       <c r="B103" t="s">
-        <v>719</v>
+        <v>889</v>
       </c>
       <c r="C103" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D103" t="s">
-        <v>488</v>
+        <v>658</v>
       </c>
       <c r="E103" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F103" t="s">
-        <v>720</v>
+        <v>890</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>721</v>
+        <v>891</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>722</v>
+        <v>892</v>
       </c>
       <c r="B104" t="s">
-        <v>723</v>
+        <v>893</v>
       </c>
       <c r="C104" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D104" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E104" t="s">
-        <v>377</v>
+        <v>547</v>
       </c>
       <c r="F104" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>724</v>
+        <v>894</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>725</v>
+        <v>895</v>
       </c>
       <c r="B105" t="s">
-        <v>726</v>
+        <v>896</v>
       </c>
       <c r="C105" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D105" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E105" t="s">
-        <v>727</v>
+        <v>897</v>
       </c>
       <c r="F105" t="s">
-        <v>728</v>
+        <v>898</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>729</v>
+        <v>899</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>730</v>
+        <v>900</v>
       </c>
       <c r="B106" t="s">
-        <v>731</v>
+        <v>901</v>
       </c>
       <c r="C106" t="s">
-        <v>732</v>
+        <v>902</v>
       </c>
       <c r="D106" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E106" t="s">
-        <v>733</v>
+        <v>903</v>
       </c>
       <c r="F106" t="s">
-        <v>262</v>
+        <v>433</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>734</v>
+        <v>904</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>735</v>
+        <v>905</v>
       </c>
       <c r="B107" t="s">
-        <v>736</v>
+        <v>906</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D107" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E107" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F107" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>737</v>
+        <v>907</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>738</v>
+        <v>908</v>
       </c>
       <c r="B108" t="s">
-        <v>739</v>
+        <v>909</v>
       </c>
       <c r="C108" t="s">
-        <v>253</v>
+        <v>424</v>
       </c>
       <c r="D108" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E108" t="s">
-        <v>740</v>
+        <v>910</v>
       </c>
       <c r="F108" t="s">
-        <v>741</v>
+        <v>911</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>742</v>
+        <v>912</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>743</v>
+        <v>913</v>
       </c>
       <c r="B109" t="s">
-        <v>744</v>
+        <v>914</v>
       </c>
       <c r="C109" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="D109" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E109" t="s">
-        <v>745</v>
+        <v>915</v>
       </c>
       <c r="F109" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>746</v>
+        <v>916</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>747</v>
+        <v>917</v>
       </c>
       <c r="B110" t="s">
-        <v>602</v>
+        <v>772</v>
       </c>
       <c r="C110" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D110" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E110" t="s">
-        <v>748</v>
+        <v>918</v>
       </c>
       <c r="F110" t="s">
-        <v>604</v>
+        <v>774</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>749</v>
+        <v>919</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>750</v>
+        <v>331</v>
       </c>
       <c r="B111" t="s">
-        <v>751</v>
+        <v>920</v>
       </c>
       <c r="C111" t="s">
-        <v>481</v>
+        <v>651</v>
       </c>
       <c r="D111" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E111" t="s">
-        <v>752</v>
+        <v>921</v>
       </c>
       <c r="F111" t="s">
-        <v>753</v>
+        <v>922</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>754</v>
+        <v>923</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>755</v>
+        <v>924</v>
       </c>
       <c r="B112" t="s">
-        <v>288</v>
+        <v>458</v>
       </c>
       <c r="C112" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D112" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E112" t="s">
-        <v>756</v>
+        <v>925</v>
       </c>
       <c r="F112" t="s">
-        <v>291</v>
+        <v>461</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>757</v>
+        <v>926</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>758</v>
+        <v>927</v>
       </c>
       <c r="B113" t="s">
-        <v>759</v>
+        <v>928</v>
       </c>
       <c r="C113" t="s">
-        <v>760</v>
+        <v>929</v>
       </c>
       <c r="D113" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E113" t="s">
-        <v>761</v>
+        <v>930</v>
       </c>
       <c r="F113" t="s">
-        <v>762</v>
+        <v>931</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>763</v>
+        <v>932</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>764</v>
+        <v>333</v>
       </c>
       <c r="B114" t="s">
-        <v>765</v>
+        <v>933</v>
       </c>
       <c r="C114" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D114" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E114" t="s">
-        <v>766</v>
+        <v>934</v>
       </c>
       <c r="F114" t="s">
-        <v>767</v>
+        <v>935</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>768</v>
+        <v>936</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>764</v>
+        <v>333</v>
       </c>
       <c r="B115" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C115" t="s">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="D115" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E115" t="s">
-        <v>769</v>
+        <v>937</v>
       </c>
       <c r="F115" t="s">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>770</v>
+        <v>938</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>771</v>
+        <v>939</v>
       </c>
       <c r="B116" t="s">
-        <v>772</v>
+        <v>940</v>
       </c>
       <c r="C116" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D116" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E116" t="s">
-        <v>773</v>
+        <v>941</v>
       </c>
       <c r="F116" t="s">
-        <v>774</v>
+        <v>942</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>775</v>
+        <v>943</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>776</v>
+        <v>944</v>
       </c>
       <c r="B117" t="s">
-        <v>777</v>
+        <v>945</v>
       </c>
       <c r="C117" t="s">
-        <v>778</v>
+        <v>946</v>
       </c>
       <c r="D117" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E117" t="s">
-        <v>779</v>
+        <v>947</v>
       </c>
       <c r="F117" t="s">
-        <v>780</v>
+        <v>948</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>781</v>
+        <v>949</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>782</v>
+        <v>950</v>
       </c>
       <c r="B118" t="s">
-        <v>783</v>
+        <v>951</v>
       </c>
       <c r="C118" t="s">
-        <v>784</v>
+        <v>952</v>
       </c>
       <c r="D118" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E118" t="s">
-        <v>785</v>
+        <v>953</v>
       </c>
       <c r="F118" t="s">
-        <v>786</v>
+        <v>954</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>787</v>
+        <v>955</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>788</v>
+        <v>956</v>
       </c>
       <c r="B119" t="s">
-        <v>789</v>
+        <v>957</v>
       </c>
       <c r="C119" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="D119" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E119" t="s">
-        <v>790</v>
+        <v>958</v>
       </c>
       <c r="F119" t="s">
-        <v>791</v>
+        <v>959</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>792</v>
+        <v>960</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>793</v>
+        <v>961</v>
       </c>
       <c r="B120" t="s">
-        <v>794</v>
+        <v>962</v>
       </c>
       <c r="C120" t="s">
-        <v>795</v>
+        <v>963</v>
       </c>
       <c r="D120" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E120" t="s">
-        <v>796</v>
+        <v>964</v>
       </c>
       <c r="F120" t="s">
-        <v>631</v>
+        <v>801</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>797</v>
+        <v>965</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>798</v>
+        <v>966</v>
       </c>
       <c r="B121" t="s">
-        <v>799</v>
+        <v>967</v>
       </c>
       <c r="C121" t="s">
-        <v>800</v>
+        <v>968</v>
       </c>
       <c r="D121" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E121" t="s">
-        <v>801</v>
+        <v>969</v>
       </c>
       <c r="F121" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>802</v>
+        <v>970</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>803</v>
+        <v>971</v>
       </c>
       <c r="B122" t="s">
-        <v>804</v>
+        <v>972</v>
       </c>
       <c r="C122" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D122" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E122" t="s">
-        <v>805</v>
+        <v>973</v>
       </c>
       <c r="F122" t="s">
-        <v>586</v>
+        <v>756</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>806</v>
+        <v>974</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>807</v>
+        <v>975</v>
       </c>
       <c r="B123" t="s">
-        <v>739</v>
+        <v>909</v>
       </c>
       <c r="C123" t="s">
-        <v>253</v>
+        <v>424</v>
       </c>
       <c r="D123" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E123" t="s">
-        <v>808</v>
+        <v>976</v>
       </c>
       <c r="F123" t="s">
-        <v>809</v>
+        <v>977</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>810</v>
+        <v>978</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>811</v>
+        <v>979</v>
       </c>
       <c r="B124" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C124" t="s">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="D124" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E124" t="s">
-        <v>812</v>
+        <v>980</v>
       </c>
       <c r="F124" t="s">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>813</v>
+        <v>981</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>814</v>
+        <v>982</v>
       </c>
       <c r="B125" t="s">
-        <v>815</v>
+        <v>983</v>
       </c>
       <c r="C125" t="s">
-        <v>816</v>
+        <v>984</v>
       </c>
       <c r="D125" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E125" t="s">
-        <v>817</v>
+        <v>985</v>
       </c>
       <c r="F125" t="s">
-        <v>818</v>
+        <v>986</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>819</v>
+        <v>987</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>820</v>
+        <v>988</v>
       </c>
       <c r="B126" t="s">
-        <v>821</v>
+        <v>989</v>
       </c>
       <c r="C126" t="s">
-        <v>822</v>
+        <v>990</v>
       </c>
       <c r="D126" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E126" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F126" t="s">
-        <v>823</v>
+        <v>991</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>824</v>
+        <v>992</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>825</v>
+        <v>993</v>
       </c>
       <c r="B127" t="s">
-        <v>826</v>
+        <v>994</v>
       </c>
       <c r="C127" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D127" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E127" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F127" t="s">
-        <v>827</v>
+        <v>995</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>828</v>
+        <v>996</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>829</v>
+        <v>997</v>
       </c>
       <c r="B128" t="s">
-        <v>830</v>
+        <v>998</v>
       </c>
       <c r="C128" t="s">
-        <v>831</v>
+        <v>999</v>
       </c>
       <c r="D128" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E128" t="s">
-        <v>832</v>
+        <v>1000</v>
       </c>
       <c r="F128" t="s">
-        <v>833</v>
+        <v>1001</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>834</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>835</v>
+        <v>1003</v>
       </c>
       <c r="B129" t="s">
-        <v>836</v>
+        <v>1004</v>
       </c>
       <c r="C129" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="D129" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E129" t="s">
-        <v>837</v>
+        <v>1005</v>
       </c>
       <c r="F129" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>838</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>839</v>
+        <v>1007</v>
       </c>
       <c r="B130" t="s">
-        <v>840</v>
+        <v>1008</v>
       </c>
       <c r="C130" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D130" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E130" t="s">
-        <v>540</v>
+        <v>710</v>
       </c>
       <c r="F130" t="s">
-        <v>841</v>
+        <v>1009</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>842</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>843</v>
+        <v>1011</v>
       </c>
       <c r="B131" t="s">
-        <v>844</v>
+        <v>1012</v>
       </c>
       <c r="C131" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D131" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E131" t="s">
-        <v>845</v>
+        <v>1013</v>
       </c>
       <c r="F131" t="s">
-        <v>846</v>
+        <v>1014</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>847</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>848</v>
+        <v>1016</v>
       </c>
       <c r="B132" t="s">
-        <v>849</v>
+        <v>338</v>
       </c>
       <c r="C132" t="s">
-        <v>850</v>
+        <v>1017</v>
       </c>
       <c r="D132" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E132" t="s">
-        <v>851</v>
+        <v>1018</v>
       </c>
       <c r="F132" t="s">
-        <v>852</v>
+        <v>1019</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>853</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>854</v>
+        <v>1021</v>
       </c>
       <c r="B133" t="s">
-        <v>855</v>
+        <v>1022</v>
       </c>
       <c r="C133" t="s">
-        <v>850</v>
+        <v>1017</v>
       </c>
       <c r="D133" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E133" t="s">
-        <v>856</v>
+        <v>1023</v>
       </c>
       <c r="F133" t="s">
-        <v>857</v>
+        <v>1024</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>858</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>859</v>
+        <v>1026</v>
       </c>
       <c r="B134" t="s">
-        <v>860</v>
+        <v>1027</v>
       </c>
       <c r="C134" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D134" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E134" t="s">
-        <v>861</v>
+        <v>1028</v>
       </c>
       <c r="F134" t="s">
-        <v>862</v>
+        <v>1029</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>863</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>864</v>
+        <v>1031</v>
       </c>
       <c r="B135" t="s">
-        <v>865</v>
+        <v>1032</v>
       </c>
       <c r="C135" t="s">
-        <v>866</v>
+        <v>1033</v>
       </c>
       <c r="D135" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E135" t="s">
-        <v>867</v>
+        <v>1034</v>
       </c>
       <c r="F135" t="s">
-        <v>367</v>
+        <v>537</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>868</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>869</v>
+        <v>1036</v>
       </c>
       <c r="B136" t="s">
-        <v>870</v>
+        <v>1037</v>
       </c>
       <c r="C136" t="s">
-        <v>871</v>
+        <v>1038</v>
       </c>
       <c r="D136" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E136" t="s">
-        <v>872</v>
+        <v>1039</v>
       </c>
       <c r="F136" t="s">
-        <v>873</v>
+        <v>1040</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>874</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>875</v>
+        <v>1042</v>
       </c>
       <c r="B137" t="s">
-        <v>844</v>
+        <v>1012</v>
       </c>
       <c r="C137" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D137" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E137" t="s">
-        <v>769</v>
+        <v>937</v>
       </c>
       <c r="F137" t="s">
-        <v>846</v>
+        <v>1014</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>876</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>877</v>
+        <v>1044</v>
       </c>
       <c r="B138" t="s">
-        <v>878</v>
+        <v>1045</v>
       </c>
       <c r="C138" t="s">
-        <v>879</v>
+        <v>1046</v>
       </c>
       <c r="D138" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E138" t="s">
-        <v>880</v>
+        <v>1047</v>
       </c>
       <c r="F138" t="s">
-        <v>881</v>
+        <v>1048</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>882</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>883</v>
+        <v>1050</v>
       </c>
       <c r="B139" t="s">
-        <v>884</v>
+        <v>1051</v>
       </c>
       <c r="C139" t="s">
-        <v>394</v>
+        <v>564</v>
       </c>
       <c r="D139" t="s">
-        <v>488</v>
+        <v>658</v>
       </c>
       <c r="E139" t="s">
-        <v>885</v>
+        <v>1052</v>
       </c>
       <c r="F139" t="s">
-        <v>886</v>
+        <v>1053</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>887</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>888</v>
+        <v>1055</v>
       </c>
       <c r="B140" t="s">
-        <v>751</v>
+        <v>920</v>
       </c>
       <c r="C140" t="s">
-        <v>481</v>
+        <v>651</v>
       </c>
       <c r="D140" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E140" t="s">
-        <v>889</v>
+        <v>1056</v>
       </c>
       <c r="F140" t="s">
-        <v>890</v>
+        <v>1057</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>891</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>892</v>
+        <v>1059</v>
       </c>
       <c r="B141" t="s">
-        <v>399</v>
+        <v>569</v>
       </c>
       <c r="C141" t="s">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="D141" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E141" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F141" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>893</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>894</v>
+        <v>1061</v>
       </c>
       <c r="B142" t="s">
-        <v>836</v>
+        <v>1004</v>
       </c>
       <c r="C142" t="s">
-        <v>301</v>
+        <v>471</v>
       </c>
       <c r="D142" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E142" t="s">
-        <v>837</v>
+        <v>1005</v>
       </c>
       <c r="F142" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>895</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>896</v>
+        <v>1063</v>
       </c>
       <c r="B143" t="s">
-        <v>897</v>
+        <v>1064</v>
       </c>
       <c r="C143" t="s">
-        <v>898</v>
+        <v>1065</v>
       </c>
       <c r="D143" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E143" t="s">
-        <v>899</v>
+        <v>1066</v>
       </c>
       <c r="F143" t="s">
-        <v>586</v>
+        <v>756</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>900</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>901</v>
+        <v>1068</v>
       </c>
       <c r="B144" t="s">
-        <v>713</v>
+        <v>883</v>
       </c>
       <c r="C144" t="s">
-        <v>714</v>
+        <v>884</v>
       </c>
       <c r="D144" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E144" t="s">
-        <v>902</v>
+        <v>1069</v>
       </c>
       <c r="F144" t="s">
-        <v>716</v>
+        <v>886</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>903</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>904</v>
+        <v>1071</v>
       </c>
       <c r="B145" t="s">
-        <v>259</v>
+        <v>430</v>
       </c>
       <c r="C145" t="s">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="D145" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E145" t="s">
-        <v>290</v>
+        <v>460</v>
       </c>
       <c r="F145" t="s">
-        <v>262</v>
+        <v>433</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>905</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>906</v>
+        <v>1073</v>
       </c>
       <c r="B146" t="s">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="C146" t="s">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="D146" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E146" t="s">
-        <v>296</v>
+        <v>466</v>
       </c>
       <c r="F146" t="s">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>907</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>908</v>
+        <v>1075</v>
       </c>
       <c r="B147" t="s">
-        <v>909</v>
+        <v>1076</v>
       </c>
       <c r="C147" t="s">
-        <v>871</v>
+        <v>1038</v>
       </c>
       <c r="D147" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E147" t="s">
-        <v>910</v>
+        <v>1077</v>
       </c>
       <c r="F147" t="s">
-        <v>911</v>
+        <v>1078</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>912</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>913</v>
+        <v>1080</v>
       </c>
       <c r="B148" t="s">
-        <v>914</v>
+        <v>1081</v>
       </c>
       <c r="C148" t="s">
-        <v>915</v>
+        <v>1082</v>
       </c>
       <c r="D148" t="s">
-        <v>488</v>
+        <v>658</v>
       </c>
       <c r="E148" t="s">
-        <v>916</v>
+        <v>1083</v>
       </c>
       <c r="F148" t="s">
-        <v>348</v>
+        <v>518</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>917</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>918</v>
+        <v>1085</v>
       </c>
       <c r="B149" t="s">
-        <v>661</v>
+        <v>831</v>
       </c>
       <c r="C149" t="s">
-        <v>662</v>
+        <v>832</v>
       </c>
       <c r="D149" t="s">
-        <v>279</v>
+        <v>449</v>
       </c>
       <c r="E149" t="s">
-        <v>919</v>
+        <v>1086</v>
       </c>
       <c r="F149" t="s">
-        <v>291</v>
+        <v>461</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>920</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>921</v>
+        <v>1088</v>
       </c>
       <c r="B150" t="s">
-        <v>399</v>
+        <v>569</v>
       </c>
       <c r="C150" t="s">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="D150" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E150" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F150" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>922</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>923</v>
+        <v>1090</v>
       </c>
       <c r="B151" t="s">
-        <v>924</v>
+        <v>1091</v>
       </c>
       <c r="C151" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D151" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E151" t="s">
-        <v>925</v>
+        <v>1092</v>
       </c>
       <c r="F151" t="s">
-        <v>926</v>
+        <v>1093</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>927</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>928</v>
+        <v>1095</v>
       </c>
       <c r="B152" t="s">
-        <v>929</v>
+        <v>1096</v>
       </c>
       <c r="C152" t="s">
-        <v>539</v>
+        <v>709</v>
       </c>
       <c r="D152" t="s">
-        <v>383</v>
+        <v>553</v>
       </c>
       <c r="E152" t="s">
-        <v>930</v>
+        <v>1097</v>
       </c>
       <c r="F152" t="s">
-        <v>268</v>
+        <v>439</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>931</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>932</v>
+        <v>1099</v>
       </c>
       <c r="B153" t="s">
-        <v>933</v>
+        <v>1100</v>
       </c>
       <c r="C153" t="s">
-        <v>850</v>
+        <v>1017</v>
       </c>
       <c r="D153" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E153" t="s">
-        <v>934</v>
+        <v>1101</v>
       </c>
       <c r="F153" t="s">
-        <v>668</v>
+        <v>838</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>935</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>936</v>
+        <v>1103</v>
       </c>
       <c r="B154" t="s">
-        <v>937</v>
+        <v>1104</v>
       </c>
       <c r="C154" t="s">
-        <v>481</v>
+        <v>651</v>
       </c>
       <c r="D154" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E154" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="F154" t="s">
-        <v>926</v>
+        <v>1093</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>938</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>939</v>
+        <v>1106</v>
       </c>
       <c r="B155" t="s">
-        <v>940</v>
+        <v>1107</v>
       </c>
       <c r="C155" t="s">
-        <v>941</v>
+        <v>1108</v>
       </c>
       <c r="D155" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="E155" t="s">
-        <v>942</v>
+        <v>1109</v>
       </c>
       <c r="F155" t="s">
-        <v>943</v>
+        <v>1110</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>944</v>
+        <v>1111</v>
       </c>
     </row>
   </sheetData>
